--- a/data/trans_orig/IP1020-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1020-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98565</t>
+          <t>99009</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103725</t>
+          <t>103724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94560</t>
+          <t>94385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>195619</t>
+          <t>195655</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83513</t>
+          <t>83499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170640</t>
+          <t>170705</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61696</t>
+          <t>63499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94547</t>
+          <t>94591</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161098</t>
+          <t>160443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166054</t>
+          <t>166052</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197808</t>
+          <t>197445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>195331</t>
+          <t>196550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201426</t>
+          <t>201425</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396821</t>
+          <t>396322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>402130</t>
+          <t>402153</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100250</t>
+          <t>100496</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122711</t>
+          <t>122756</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225411</t>
+          <t>226259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69922</t>
+          <t>70052</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142944</t>
+          <t>142773</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>628626</t>
+          <t>629072</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>636730</t>
+          <t>636775</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>674098</t>
+          <t>673316</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681632</t>
+          <t>681485</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1305783</t>
+          <t>1306385</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1316694</t>
+          <t>1316742</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84384</t>
+          <t>84693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85819</t>
+          <t>85878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172432</t>
+          <t>172011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177557</t>
+          <t>177556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86326</t>
+          <t>86454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92056</t>
+          <t>92055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182848</t>
+          <t>183062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188168</t>
+          <t>188169</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78913</t>
+          <t>78607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83584</t>
+          <t>83585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83844</t>
+          <t>83352</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165120</t>
+          <t>164506</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>170424</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196190</t>
+          <t>196621</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203818</t>
+          <t>203887</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221390</t>
+          <t>220504</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>226247</t>
+          <t>226238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>421005</t>
+          <t>420717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>429852</t>
+          <t>429699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>758</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141303</t>
+          <t>140636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147729</t>
+          <t>147580</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133233</t>
+          <t>133210</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139124</t>
+          <t>139076</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>276954</t>
+          <t>277587</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>285727</t>
+          <t>285685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>733</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>455</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9680</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47264</t>
+          <t>46825</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53188</t>
+          <t>53178</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68322</t>
+          <t>68174</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73581</t>
+          <t>73583</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118269</t>
+          <t>118839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125817</t>
+          <t>125861</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24502</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14493</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34453</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649579</t>
+          <t>650310</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>663019</t>
+          <t>663429</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>699008</t>
+          <t>699055</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>708573</t>
+          <t>708406</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1353129</t>
+          <t>1353108</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1369599</t>
+          <t>1368964</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77288</t>
+          <t>76967</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82477</t>
+          <t>82480</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91870</t>
+          <t>91981</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98473</t>
+          <t>98444</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172020</t>
+          <t>172190</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>179945</t>
+          <t>180108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105935</t>
+          <t>105570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112077</t>
+          <t>112082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211115</t>
+          <t>211905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217798</t>
+          <t>217799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70537</t>
+          <t>71170</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132572</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214738</t>
+          <t>215574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>221490</t>
+          <t>221921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>206048</t>
+          <t>205378</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>424399</t>
+          <t>424085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431857</t>
+          <t>431730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131063</t>
+          <t>131327</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>139051</t>
+          <t>138936</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272549</t>
+          <t>272011</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57914</t>
+          <t>57959</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61952</t>
+          <t>62631</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67196</t>
+          <t>67191</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122373</t>
+          <t>122314</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128261</t>
+          <t>128260</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14141</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29526</t>
+          <t>28787</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>657361</t>
+          <t>657373</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>666513</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>690687</t>
+          <t>691233</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>702270</t>
+          <t>702976</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1351713</t>
+          <t>1352452</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1366904</t>
+          <t>1366472</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16059</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94448</t>
+          <t>94955</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102238</t>
+          <t>102297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127513</t>
+          <t>127759</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135209</t>
+          <t>135376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>225311</t>
+          <t>224580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>236274</t>
+          <t>236211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87319</t>
+          <t>86814</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93517</t>
+          <t>93661</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89533</t>
+          <t>88811</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>94870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179456</t>
+          <t>179821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187797</t>
+          <t>187596</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46765</t>
+          <t>47410</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58193</t>
+          <t>57990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63387</t>
+          <t>63388</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107953</t>
+          <t>108109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114484</t>
+          <t>114534</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>13506</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21938</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>205365</t>
+          <t>205423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>214939</t>
+          <t>215038</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205037</t>
+          <t>204766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214724</t>
+          <t>214517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>414344</t>
+          <t>415294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>427855</t>
+          <t>428165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111145</t>
+          <t>110797</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117903</t>
+          <t>118013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152797</t>
+          <t>152490</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160684</t>
+          <t>161053</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>267438</t>
+          <t>267821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>277446</t>
+          <t>278085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>11971</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60493</t>
+          <t>61673</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63820</t>
+          <t>64220</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71106</t>
+          <t>71011</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129457</t>
+          <t>128927</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>138610</t>
+          <t>138515</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>14374</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30532</t>
+          <t>31083</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16481</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33511</t>
+          <t>33466</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35047</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57892</t>
+          <t>58020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>626805</t>
+          <t>626254</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>642110</t>
+          <t>642963</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>715714</t>
+          <t>715759</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>732744</t>
+          <t>732597</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1348671</t>
+          <t>1348543</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1371516</t>
+          <t>1371585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
